--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Agricultural Production - Foodgrains.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Agricultural Production - Foodgrains.xlsx
@@ -270,8 +270,8 @@
     <t>(Lakhs Tonnes)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note : Data for 2025-26   are based on First Advance Estimates.
-Also see Notes on Tables.
+    <t xml:space="preserve">Note     : Data for 2025-26 are based on Third Advance Estimates.
+              Also see Notes on Tables.
 Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
   </si>
 </sst>
@@ -484,11 +484,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:H87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="10.7125106666667" customWidth="1"/>
     <col min="3" max="8" width="17.9679986666667" customWidth="1"/>
+    <col min="9" max="9" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -571,20 +572,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="12">
-        <v>1245.04</v>
-      </c>
-      <c r="D9" s="12"/>
+        <v>1540.24</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1206.57</v>
+      </c>
       <c r="E9" s="12">
-        <v>414.14</v>
+        <v>744.72</v>
       </c>
       <c r="F9" s="12">
-        <v>1659.18</v>
+        <v>3491.54</v>
       </c>
       <c r="G9" s="12">
-        <v>74.13</v>
+        <v>274.09</v>
       </c>
       <c r="H9" s="12">
-        <v>1733.3</v>
+        <v>3765.63</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -2322,6 +2325,7 @@
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
     </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
